--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-14T06:15:19+00:00</t>
+    <t>2024-06-18T10:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:21+00:00</t>
+    <t>2024-06-18T10:57:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:59+00:00</t>
+    <t>2024-06-18T10:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:58:59+00:00</t>
+    <t>2024-06-18T11:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T11:16:13+00:00</t>
+    <t>2024-07-02T10:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(WORK))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T10:09:21+00:00</t>
+    <t>2024-09-06T16:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
+++ b/branches/prescription/StructureDefinition-VisibilityFlag.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T16:05:52+00:00</t>
+    <t>2024-10-22T10:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
